--- a/Excel/Vlookup quetions new 1.xlsx
+++ b/Excel/Vlookup quetions new 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhiw\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Arbor all Folder\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A2ABBE-A2DE-4BBE-9046-47C8F07CB901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A5C36F-9982-4355-9628-ECCF9608B345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="3" xr2:uid="{3E9A778E-4FE8-40FF-9378-4EF33D5E7F57}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{3E9A778E-4FE8-40FF-9378-4EF33D5E7F57}"/>
   </bookViews>
   <sheets>
     <sheet name="Data1" sheetId="1" r:id="rId1"/>
@@ -19,16 +19,26 @@
     <sheet name="Quetions on Data 2" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="217">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -1813,13 +1823,52 @@
       </rPr>
       <t xml:space="preserve"> for the first occurrence.</t>
     </r>
+  </si>
+  <si>
+    <t>Firstname</t>
+  </si>
+  <si>
+    <t>Lastname</t>
+  </si>
+  <si>
+    <t>EmpId</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>Emp_type</t>
+  </si>
+  <si>
+    <t>Hiredate</t>
+  </si>
+  <si>
+    <t>EmpID</t>
+  </si>
+  <si>
+    <t>anjali.reddy@company.com</t>
+  </si>
+  <si>
+    <t>Exp_yers</t>
+  </si>
+  <si>
+    <t>Sales Amount</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>SlaeID</t>
+  </si>
+  <si>
+    <t>laptop</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1851,8 +1900,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1862,6 +1919,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1986,10 +2049,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2012,45 +2076,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -2237,13 +2283,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2256,6 +2295,47 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -2272,19 +2352,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FDB5EAA5-8EAA-4D89-9C28-0A119864EB81}" name="data" displayName="data" ref="A1:J31" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="12" tableBorderDxfId="13" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FDB5EAA5-8EAA-4D89-9C28-0A119864EB81}" name="data" displayName="data" ref="A1:J31" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="A1:J31" xr:uid="{FDB5EAA5-8EAA-4D89-9C28-0A119864EB81}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A555F1C3-58E1-457F-8416-82816D0A94A7}" name="SaleID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{73216928-D981-4D7F-A9F7-97F4C9979527}" name="OrderDate" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{13B9E53E-D2CC-4F7A-9259-B92C5E2E01F9}" name="CustomerName" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{0D469982-0FA8-43FF-8CE6-C762F28E52AE}" name="ProductName" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{CFDB60B2-4F24-48DA-8679-F16C1AB93463}" name="Category" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{CC4F0CAB-9679-4D74-8589-AE6838BB82B0}" name="Region" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{D6D0A409-E05A-48C9-93D5-CCB3CA19E07C}" name="SalesAmount" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{3AA10277-1FFE-4711-8FB9-DE58DD27C0BC}" name="Quantity" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{9C63560D-3411-4047-8438-38C6F45F0CE6}" name="PaymentMode" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{AE83D3C5-0850-459C-BFAD-D68EC8045924}" name="SalesPerson" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{A555F1C3-58E1-457F-8416-82816D0A94A7}" name="SaleID" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{73216928-D981-4D7F-A9F7-97F4C9979527}" name="OrderDate" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{13B9E53E-D2CC-4F7A-9259-B92C5E2E01F9}" name="CustomerName" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{0D469982-0FA8-43FF-8CE6-C762F28E52AE}" name="ProductName" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{CFDB60B2-4F24-48DA-8679-F16C1AB93463}" name="Category" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{CC4F0CAB-9679-4D74-8589-AE6838BB82B0}" name="Region" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{D6D0A409-E05A-48C9-93D5-CCB3CA19E07C}" name="SalesAmount" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{3AA10277-1FFE-4711-8FB9-DE58DD27C0BC}" name="Quantity" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{9C63560D-3411-4047-8438-38C6F45F0CE6}" name="PaymentMode" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{AE83D3C5-0850-459C-BFAD-D68EC8045924}" name="SalesPerson" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2590,20 +2670,19 @@
   <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5011,120 +5090,369 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43B4668F-FAAD-48B8-BEBA-C240DD5E1D75}">
-  <dimension ref="B2:B32"/>
+  <dimension ref="B2:O43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="12" max="12" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" ht="18" x14ac:dyDescent="0.3">
       <c r="B2" s="13" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L2" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="M2" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="N2" s="20" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="14"/>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L3" s="18">
+        <v>25</v>
+      </c>
+      <c r="M3" s="18" t="str">
+        <f>VLOOKUP(L3,Data1!A2:O51,2,0)</f>
+        <v>Anjali</v>
+      </c>
+      <c r="N3" s="18" t="str">
+        <f>VLOOKUP(L3,Data1!A2:O51,3,0)</f>
+        <v>Reddy</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" s="14"/>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L5" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="M5" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="N5" s="16"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="14" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L6" s="18">
+        <v>14</v>
+      </c>
+      <c r="M6" s="18" t="str">
+        <f>VLOOKUP(L6,Data1!A2:O51,6,0)</f>
+        <v>IT</v>
+      </c>
+      <c r="N6" s="16"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="14"/>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="14" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L8" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="N8" s="16"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="14"/>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L9" s="18">
+        <v>40</v>
+      </c>
+      <c r="M9" s="18">
+        <f>VLOOKUP(L9,Data1!A2:O51,8,0)</f>
+        <v>115145</v>
+      </c>
+      <c r="N9" s="16"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="14" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="14"/>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L11" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="M11" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="N11" s="16"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="14" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L12" s="18">
+        <v>7</v>
+      </c>
+      <c r="M12" s="18" t="str">
+        <f>VLOOKUP(L12,Data1!A2:O51,11,0)</f>
+        <v>Hyderabad</v>
+      </c>
+      <c r="N12" s="16"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="14"/>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="14" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L14" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="M14" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="N14" s="20" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="14"/>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L15" s="18">
+        <v>32</v>
+      </c>
+      <c r="M15" s="18" t="str">
+        <f>VLOOKUP(L15,Data1!A2:O51,7,0)</f>
+        <v>Manager</v>
+      </c>
+      <c r="N15" s="18" t="str">
+        <f>VLOOKUP(L15,Data1!A2:O51,13,0)</f>
+        <v>Part-Time</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="14" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B17" s="14"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L17" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="M17" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B18" s="14" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L18" s="18">
+        <v>13</v>
+      </c>
+      <c r="M18" s="18">
+        <f>VLOOKUP(L18,Data1!A2:O51,14,0)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B19" s="14"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B20" s="14" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L20" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="M20" s="20" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B21" s="14"/>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L21" s="18">
+        <v>5</v>
+      </c>
+      <c r="M21" s="18">
+        <f>VLOOKUP(L21,Data1!A2:O51,9,0)</f>
+        <v>45144</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B22" s="14" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="L23" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L24" s="18">
+        <v>30</v>
+      </c>
+      <c r="M24" s="18">
+        <f>VLOOKUP(L24,Data1!A2:O51,12,0)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L26" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="M26" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N26" s="20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="L27" s="18">
+        <v>47</v>
+      </c>
+      <c r="M27" s="18" t="str">
+        <f>VLOOKUP(L27,Data1!A2:O51,10,0)</f>
+        <v>arjun.sharma47@company.com</v>
+      </c>
+      <c r="N27" s="18" t="str">
+        <f>VLOOKUP(L27,Data1!A2:O51,6,0)</f>
+        <v>Finance</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="M30" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N30" s="20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="M31" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="N31" s="17"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>198</v>
       </c>
     </row>
+    <row r="33" spans="13:15" x14ac:dyDescent="0.3">
+      <c r="M33" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N33" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="O33" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="13:15" x14ac:dyDescent="0.3">
+      <c r="M34" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="N34" s="17"/>
+      <c r="O34" s="19"/>
+    </row>
+    <row r="36" spans="13:15" x14ac:dyDescent="0.3">
+      <c r="M36" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N36" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="O36" s="20" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="37" spans="13:15" x14ac:dyDescent="0.3">
+      <c r="M37" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="N37" s="17"/>
+      <c r="O37" s="19"/>
+    </row>
+    <row r="39" spans="13:15" x14ac:dyDescent="0.3">
+      <c r="M39" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N39" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="13:15" x14ac:dyDescent="0.3">
+      <c r="M40" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="N40" s="17"/>
+    </row>
+    <row r="42" spans="13:15" x14ac:dyDescent="0.3">
+      <c r="M42" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N42" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="O42" s="20" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="43" spans="13:15" x14ac:dyDescent="0.3">
+      <c r="M43" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="N43" s="17"/>
+      <c r="O43" s="19"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M31" r:id="rId1" xr:uid="{BAE03113-B150-4AEF-87F4-F46C64D80505}"/>
+    <hyperlink ref="M34" r:id="rId2" xr:uid="{75D5BDF9-C7C6-4EE5-8504-A0FA0FE34F98}"/>
+    <hyperlink ref="M37" r:id="rId3" xr:uid="{4CCB45B4-4DAD-4648-91D2-3564026052D7}"/>
+    <hyperlink ref="M40" r:id="rId4" xr:uid="{EB3C6966-6CE1-48DB-B025-5CFBE6C7DAB6}"/>
+    <hyperlink ref="M43" r:id="rId5" xr:uid="{3C6C979D-79BF-4C69-96BF-C3A3380FD4B1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6148,136 +6476,281 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A695A6-5DF7-49B7-A75E-8A02A83AF1AB}">
-  <dimension ref="B2:B33"/>
+  <dimension ref="B2:N34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="12" max="12" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" ht="23.4" x14ac:dyDescent="0.3">
       <c r="B2" s="15" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="14"/>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L3" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="14" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L4" s="18">
+        <v>12</v>
+      </c>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" s="14"/>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="14" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L6" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="14"/>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L7" s="18">
+        <v>6</v>
+      </c>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="14" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="14"/>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L9" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="14" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L10" s="18">
+        <v>19</v>
+      </c>
+      <c r="M10" s="18"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="14"/>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="14" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L12" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="M12" s="20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="14"/>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L13" s="18">
+        <v>25</v>
+      </c>
+      <c r="M13" s="18"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="14" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="14"/>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L15" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="M15" s="20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="14" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L16" s="18">
+        <v>3</v>
+      </c>
+      <c r="M16" s="18"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B17" s="14"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B18" s="14" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L18" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="M18" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="N18" s="20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B19" s="14"/>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L19" s="18">
+        <v>20</v>
+      </c>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B20" s="14" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B21" s="14"/>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L21" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="M21" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="N21" s="20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B22" s="14" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="23" spans="2:2" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L22" s="18">
+        <v>8</v>
+      </c>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+    </row>
+    <row r="23" spans="2:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="15"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24" s="14"/>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L24" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="N24" s="20" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B25" s="14" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L25" s="18">
+        <v>27</v>
+      </c>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B26" s="14"/>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B27" s="14" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L27" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="N27" s="20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B28" s="14"/>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L28" s="18">
+        <v>14</v>
+      </c>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B29" s="14" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B30" s="14"/>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L30" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="M30" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="N30" s="20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B31" s="14" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="L31" s="18">
+        <v>30</v>
+      </c>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B32" s="14"/>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="14" t="s">
         <v>203</v>
       </c>
+      <c r="L33" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="M33" s="20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="L34" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="M34" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
